--- a/filesystem/MarketingOps/Org/client_services_org_chart.xlsx
+++ b/filesystem/MarketingOps/Org/client_services_org_chart.xlsx
@@ -115,7 +115,7 @@
       <sz val="11"/>
     </font>
   </fonts>
-  <fills count="12">
+  <fills count="13">
     <fill>
       <patternFill/>
     </fill>
@@ -178,8 +178,13 @@
         <bgColor rgb="00F1F5F9"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F8FAFC"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="6">
+  <borders count="12">
     <border>
       <left/>
       <right/>
@@ -257,11 +262,79 @@
         <color rgb="002563EB"/>
       </bottom>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00E2E8F0"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00E2E8F0"/>
+      </right>
+      <top style="thin">
+        <color rgb="00E2E8F0"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00E2E8F0"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00E2E8F0"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00E2E8F0"/>
+      </right>
+      <top style="thin">
+        <color rgb="00E2E8F0"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00E2E8F0"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00E2E8F0"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="002563EB"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00E2E8F0"/>
+      </right>
+      <top style="thin">
+        <color rgb="00E2E8F0"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="002563EB"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="45">
+  <cellXfs count="56">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -391,6 +464,31 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="11" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="11" fillId="12" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="12" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="12" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="12" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="12" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="9" fillId="12" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="12" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -718,14 +816,6 @@
           <t>THORNFIELD LIFE SCIENCES MARKETING — Client Services Org Chart &amp; Contract Ownership Map</t>
         </is>
       </c>
-      <c r="B1" s="19" t="n"/>
-      <c r="C1" s="19" t="n"/>
-      <c r="D1" s="19" t="n"/>
-      <c r="E1" s="19" t="n"/>
-      <c r="F1" s="19" t="n"/>
-      <c r="G1" s="19" t="n"/>
-      <c r="H1" s="19" t="n"/>
-      <c r="I1" s="19" t="n"/>
     </row>
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="20" t="inlineStr">
@@ -738,13 +828,13 @@
           <t>/MarketingOps/Org/client_services_org_chart.xlsx</t>
         </is>
       </c>
-      <c r="C2" s="21" t="n"/>
-      <c r="D2" s="21" t="n"/>
-      <c r="E2" s="21" t="n"/>
-      <c r="F2" s="21" t="n"/>
-      <c r="G2" s="21" t="n"/>
-      <c r="H2" s="21" t="n"/>
-      <c r="I2" s="21" t="n"/>
+      <c r="C2" s="45" t="n"/>
+      <c r="D2" s="45" t="n"/>
+      <c r="E2" s="45" t="n"/>
+      <c r="F2" s="45" t="n"/>
+      <c r="G2" s="45" t="n"/>
+      <c r="H2" s="45" t="n"/>
+      <c r="I2" s="46" t="n"/>
     </row>
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="20" t="inlineStr">
@@ -757,13 +847,13 @@
           <t>Sofia Bergen, Director, Client Strategy</t>
         </is>
       </c>
-      <c r="C3" s="21" t="n"/>
-      <c r="D3" s="21" t="n"/>
-      <c r="E3" s="21" t="n"/>
-      <c r="F3" s="21" t="n"/>
-      <c r="G3" s="21" t="n"/>
-      <c r="H3" s="21" t="n"/>
-      <c r="I3" s="21" t="n"/>
+      <c r="C3" s="45" t="n"/>
+      <c r="D3" s="45" t="n"/>
+      <c r="E3" s="45" t="n"/>
+      <c r="F3" s="45" t="n"/>
+      <c r="G3" s="45" t="n"/>
+      <c r="H3" s="45" t="n"/>
+      <c r="I3" s="46" t="n"/>
     </row>
     <row r="4" ht="30" customHeight="1">
       <c r="A4" s="20" t="inlineStr">
@@ -776,13 +866,13 @@
           <t>Post-close Thornfield client-services roster: Thornfield-native accounts plus Bramwell-origin accounts migrated at 9/1/2025 close. One row per active client on the ERPNext Customer master.</t>
         </is>
       </c>
-      <c r="C4" s="21" t="n"/>
-      <c r="D4" s="21" t="n"/>
-      <c r="E4" s="21" t="n"/>
-      <c r="F4" s="21" t="n"/>
-      <c r="G4" s="21" t="n"/>
-      <c r="H4" s="21" t="n"/>
-      <c r="I4" s="21" t="n"/>
+      <c r="C4" s="45" t="n"/>
+      <c r="D4" s="45" t="n"/>
+      <c r="E4" s="45" t="n"/>
+      <c r="F4" s="45" t="n"/>
+      <c r="G4" s="45" t="n"/>
+      <c r="H4" s="45" t="n"/>
+      <c r="I4" s="46" t="n"/>
     </row>
     <row r="5" ht="22" customHeight="1">
       <c r="A5" s="20" t="inlineStr">
@@ -795,13 +885,13 @@
           <t>USD ($#,##0). Dates: MM/DD/YYYY.</t>
         </is>
       </c>
-      <c r="C5" s="21" t="n"/>
-      <c r="D5" s="21" t="n"/>
-      <c r="E5" s="21" t="n"/>
-      <c r="F5" s="21" t="n"/>
-      <c r="G5" s="21" t="n"/>
-      <c r="H5" s="21" t="n"/>
-      <c r="I5" s="21" t="n"/>
+      <c r="C5" s="45" t="n"/>
+      <c r="D5" s="45" t="n"/>
+      <c r="E5" s="45" t="n"/>
+      <c r="F5" s="45" t="n"/>
+      <c r="G5" s="45" t="n"/>
+      <c r="H5" s="45" t="n"/>
+      <c r="I5" s="46" t="n"/>
     </row>
     <row r="6" ht="12" customHeight="1"/>
     <row r="7" ht="32" customHeight="1">
@@ -2885,7 +2975,7 @@
       </c>
       <c r="C55" s="32" t="inlineStr">
         <is>
-          <t>Inherited — Bramwell</t>
+          <t>Thornfield native</t>
         </is>
       </c>
       <c r="D55" s="33" t="inlineStr">
@@ -2900,7 +2990,7 @@
       </c>
       <c r="F55" s="33" t="inlineStr">
         <is>
-          <t>% of managed spend (legacy schedule)</t>
+          <t>% of managed spend (12%)</t>
         </is>
       </c>
       <c r="G55" s="34" t="n">
@@ -2911,7 +3001,7 @@
       </c>
       <c r="I55" s="35" t="inlineStr">
         <is>
-          <t>Bramwell-era MSA in force through original expiry; ongoing under Thornfield standard billing.</t>
+          <t>Renewed 03/12/2023; ongoing under Thornfield standard billing.</t>
         </is>
       </c>
     </row>
@@ -2928,7 +3018,7 @@
       </c>
       <c r="C56" s="26" t="inlineStr">
         <is>
-          <t>Inherited — Bramwell</t>
+          <t>Thornfield native</t>
         </is>
       </c>
       <c r="D56" s="27" t="inlineStr">
@@ -2954,14 +3044,14 @@
       </c>
       <c r="I56" s="29" t="inlineStr">
         <is>
-          <t>Bramwell-era MSA in force through original expiry; reassigned at close, no scope change.</t>
+          <t>Renewed 07/01/2024 under 24-month SOP.</t>
         </is>
       </c>
     </row>
     <row r="57" ht="24" customHeight="1">
       <c r="A57" s="30" t="inlineStr">
         <is>
-          <t>CUST-2025-0058</t>
+          <t>CUST-2025-0358</t>
         </is>
       </c>
       <c r="B57" s="31" t="inlineStr">
@@ -3057,7 +3147,7 @@
       </c>
       <c r="C59" s="32" t="inlineStr">
         <is>
-          <t>Inherited — Bramwell</t>
+          <t>Thornfield native</t>
         </is>
       </c>
       <c r="D59" s="33" t="inlineStr">
@@ -3072,7 +3162,7 @@
       </c>
       <c r="F59" s="33" t="inlineStr">
         <is>
-          <t>% of managed spend (legacy schedule)</t>
+          <t>% of managed spend (12%)</t>
         </is>
       </c>
       <c r="G59" s="34" t="n">
@@ -3143,7 +3233,7 @@
       </c>
       <c r="C61" s="32" t="inlineStr">
         <is>
-          <t>Inherited — Bramwell</t>
+          <t>Thornfield native</t>
         </is>
       </c>
       <c r="D61" s="33" t="inlineStr">
@@ -3169,7 +3259,7 @@
       </c>
       <c r="I61" s="35" t="inlineStr">
         <is>
-          <t>Bramwell-era attribution methodology retired at close; MSA in force through original expiry.</t>
+          <t>Renewed 08/01/2024; ongoing under Thornfield standard billing.</t>
         </is>
       </c>
     </row>
@@ -3647,43 +3737,43 @@
       </c>
     </row>
     <row r="73" ht="24" customHeight="1">
-      <c r="A73" s="36" t="inlineStr">
+      <c r="A73" s="49" t="inlineStr">
         <is>
           <t>CUST-2025-0198</t>
         </is>
       </c>
-      <c r="B73" s="37" t="inlineStr">
+      <c r="B73" s="50" t="inlineStr">
         <is>
           <t>Fenwick Genomics</t>
         </is>
       </c>
-      <c r="C73" s="38" t="inlineStr">
+      <c r="C73" s="51" t="inlineStr">
         <is>
           <t>Inherited — Bramwell</t>
         </is>
       </c>
-      <c r="D73" s="39" t="inlineStr">
+      <c r="D73" s="52" t="inlineStr">
         <is>
           <t>Sofia Bergen</t>
         </is>
       </c>
-      <c r="E73" s="40" t="inlineStr">
+      <c r="E73" s="53" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="F73" s="39" t="inlineStr">
+      <c r="F73" s="52" t="inlineStr">
         <is>
           <t>Flat monthly retainer $8,500</t>
         </is>
       </c>
-      <c r="G73" s="41" t="n">
+      <c r="G73" s="54" t="n">
         <v>45748</v>
       </c>
-      <c r="H73" s="41" t="n">
+      <c r="H73" s="54" t="n">
         <v>46112</v>
       </c>
-      <c r="I73" s="42" t="inlineStr">
+      <c r="I73" s="55" t="inlineStr">
         <is>
           <t>ERPNext Sales Order of record SO-2025-0417; consult /Legal/Legacy_Bramwell/ for full contract terms.</t>
         </is>
@@ -3739,14 +3829,14 @@
           <t>Notes on maintenance</t>
         </is>
       </c>
-      <c r="B76" s="44" t="n"/>
-      <c r="C76" s="44" t="n"/>
-      <c r="D76" s="44" t="n"/>
-      <c r="E76" s="44" t="n"/>
-      <c r="F76" s="44" t="n"/>
-      <c r="G76" s="44" t="n"/>
-      <c r="H76" s="44" t="n"/>
-      <c r="I76" s="44" t="n"/>
+      <c r="B76" s="47" t="n"/>
+      <c r="C76" s="47" t="n"/>
+      <c r="D76" s="47" t="n"/>
+      <c r="E76" s="47" t="n"/>
+      <c r="F76" s="47" t="n"/>
+      <c r="G76" s="47" t="n"/>
+      <c r="H76" s="47" t="n"/>
+      <c r="I76" s="48" t="n"/>
     </row>
     <row r="77" ht="24" customHeight="1">
       <c r="A77" s="35" t="inlineStr">
@@ -3754,14 +3844,14 @@
           <t>• Account Origin values match the ERPNext Customer master `account_origin` field, set at the 08/25/2025 migration cutover.</t>
         </is>
       </c>
-      <c r="B77" s="35" t="n"/>
-      <c r="C77" s="35" t="n"/>
-      <c r="D77" s="35" t="n"/>
-      <c r="E77" s="35" t="n"/>
-      <c r="F77" s="35" t="n"/>
-      <c r="G77" s="35" t="n"/>
-      <c r="H77" s="35" t="n"/>
-      <c r="I77" s="35" t="n"/>
+      <c r="B77" s="45" t="n"/>
+      <c r="C77" s="45" t="n"/>
+      <c r="D77" s="45" t="n"/>
+      <c r="E77" s="45" t="n"/>
+      <c r="F77" s="45" t="n"/>
+      <c r="G77" s="45" t="n"/>
+      <c r="H77" s="45" t="n"/>
+      <c r="I77" s="46" t="n"/>
     </row>
     <row r="78" ht="28" customHeight="1">
       <c r="A78" s="35" t="inlineStr">
@@ -3769,14 +3859,14 @@
           <t>• Current AM reflects post-close ownership as recorded in ERPNext; Bramwell-origin reassignments are cross-referenced against the client-services account transition log.</t>
         </is>
       </c>
-      <c r="B78" s="35" t="n"/>
-      <c r="C78" s="35" t="n"/>
-      <c r="D78" s="35" t="n"/>
-      <c r="E78" s="35" t="n"/>
-      <c r="F78" s="35" t="n"/>
-      <c r="G78" s="35" t="n"/>
-      <c r="H78" s="35" t="n"/>
-      <c r="I78" s="35" t="n"/>
+      <c r="B78" s="45" t="n"/>
+      <c r="C78" s="45" t="n"/>
+      <c r="D78" s="45" t="n"/>
+      <c r="E78" s="45" t="n"/>
+      <c r="F78" s="45" t="n"/>
+      <c r="G78" s="45" t="n"/>
+      <c r="H78" s="45" t="n"/>
+      <c r="I78" s="46" t="n"/>
     </row>
     <row r="79" ht="42" customHeight="1">
       <c r="A79" s="35" t="inlineStr">
@@ -3784,14 +3874,14 @@
           <t>• "Bramwell Founder Relationship" flags accounts where the founding client relationship was personally held by Marcus Oyelaran in his pre-close founder capacity. Only Fenwick Genomics carries this flag; other Bramwell-origin accounts were owned by pre-close Bramwell account managers rather than the founder.</t>
         </is>
       </c>
-      <c r="B79" s="35" t="n"/>
-      <c r="C79" s="35" t="n"/>
-      <c r="D79" s="35" t="n"/>
-      <c r="E79" s="35" t="n"/>
-      <c r="F79" s="35" t="n"/>
-      <c r="G79" s="35" t="n"/>
-      <c r="H79" s="35" t="n"/>
-      <c r="I79" s="35" t="n"/>
+      <c r="B79" s="45" t="n"/>
+      <c r="C79" s="45" t="n"/>
+      <c r="D79" s="45" t="n"/>
+      <c r="E79" s="45" t="n"/>
+      <c r="F79" s="45" t="n"/>
+      <c r="G79" s="45" t="n"/>
+      <c r="H79" s="45" t="n"/>
+      <c r="I79" s="46" t="n"/>
     </row>
     <row r="80" ht="28" customHeight="1">
       <c r="A80" s="35" t="inlineStr">
@@ -3799,29 +3889,29 @@
           <t>• MSA Effective and MSA Expiry dates are recorded as originally executed and do not reset on account transition or reassignment. Renewals seated at a client's renewal date are tracked in the transition log and in ERPNext Sales Orders.</t>
         </is>
       </c>
-      <c r="B80" s="35" t="n"/>
-      <c r="C80" s="35" t="n"/>
-      <c r="D80" s="35" t="n"/>
-      <c r="E80" s="35" t="n"/>
-      <c r="F80" s="35" t="n"/>
-      <c r="G80" s="35" t="n"/>
-      <c r="H80" s="35" t="n"/>
-      <c r="I80" s="35" t="n"/>
+      <c r="B80" s="45" t="n"/>
+      <c r="C80" s="45" t="n"/>
+      <c r="D80" s="45" t="n"/>
+      <c r="E80" s="45" t="n"/>
+      <c r="F80" s="45" t="n"/>
+      <c r="G80" s="45" t="n"/>
+      <c r="H80" s="45" t="n"/>
+      <c r="I80" s="46" t="n"/>
     </row>
     <row r="81" ht="56" customHeight="1">
       <c r="A81" s="35" t="inlineStr">
         <is>
-          <t>• Contract Type "% of managed spend (12%)" reflects the Thornfield rate card (A03) effective 9/1/2025 for ongoing billing on percentage-based Thornfield-native accounts. "% of managed spend (legacy schedule)" reflects the legacy-accounts renewal-rate schedule (A08 through 12/09/2025; A09 from 12/10/2025 forward) applicable at each inherited account's renewal date. Flat monthly retainers reflect the executed MSA amount.</t>
-        </is>
-      </c>
-      <c r="B81" s="35" t="n"/>
-      <c r="C81" s="35" t="n"/>
-      <c r="D81" s="35" t="n"/>
-      <c r="E81" s="35" t="n"/>
-      <c r="F81" s="35" t="n"/>
-      <c r="G81" s="35" t="n"/>
-      <c r="H81" s="35" t="n"/>
-      <c r="I81" s="35" t="n"/>
+          <t>• Contract Type "% of managed spend (12%)" reflects the Thornfield Rate Card (Management Fee &amp; Discount Schedule) effective 9/1/2025 for ongoing billing on percentage-based Thornfield-native accounts. "% of managed spend (legacy schedule)" reflects the legacy-accounts renewal-rate schedule (11% through 12/09/2025; 13% from 12/10/2025 forward) applicable at each inherited account's renewal date. Flat monthly retainers reflect the executed MSA amount.</t>
+        </is>
+      </c>
+      <c r="B81" s="45" t="n"/>
+      <c r="C81" s="45" t="n"/>
+      <c r="D81" s="45" t="n"/>
+      <c r="E81" s="45" t="n"/>
+      <c r="F81" s="45" t="n"/>
+      <c r="G81" s="45" t="n"/>
+      <c r="H81" s="45" t="n"/>
+      <c r="I81" s="46" t="n"/>
     </row>
     <row r="82" ht="12" customHeight="1"/>
     <row r="83" ht="28" customHeight="1">
@@ -3830,14 +3920,14 @@
           <t>Sign-off</t>
         </is>
       </c>
-      <c r="B83" s="44" t="n"/>
-      <c r="C83" s="44" t="n"/>
-      <c r="D83" s="44" t="n"/>
-      <c r="E83" s="44" t="n"/>
-      <c r="F83" s="44" t="n"/>
-      <c r="G83" s="44" t="n"/>
-      <c r="H83" s="44" t="n"/>
-      <c r="I83" s="44" t="n"/>
+      <c r="B83" s="47" t="n"/>
+      <c r="C83" s="47" t="n"/>
+      <c r="D83" s="47" t="n"/>
+      <c r="E83" s="47" t="n"/>
+      <c r="F83" s="47" t="n"/>
+      <c r="G83" s="47" t="n"/>
+      <c r="H83" s="47" t="n"/>
+      <c r="I83" s="48" t="n"/>
     </row>
     <row r="84" ht="22" customHeight="1">
       <c r="A84" s="20" t="inlineStr">
@@ -3850,13 +3940,13 @@
           <t>Sofia Bergen, Director, Client Strategy</t>
         </is>
       </c>
-      <c r="C84" s="33" t="n"/>
-      <c r="D84" s="33" t="n"/>
-      <c r="E84" s="33" t="n"/>
-      <c r="F84" s="33" t="n"/>
-      <c r="G84" s="33" t="n"/>
-      <c r="H84" s="33" t="n"/>
-      <c r="I84" s="33" t="n"/>
+      <c r="C84" s="45" t="n"/>
+      <c r="D84" s="45" t="n"/>
+      <c r="E84" s="45" t="n"/>
+      <c r="F84" s="45" t="n"/>
+      <c r="G84" s="45" t="n"/>
+      <c r="H84" s="45" t="n"/>
+      <c r="I84" s="46" t="n"/>
     </row>
     <row r="85" ht="22" customHeight="1">
       <c r="A85" s="20" t="inlineStr">
@@ -3869,13 +3959,13 @@
           <t>01/05/2026</t>
         </is>
       </c>
-      <c r="C85" s="33" t="n"/>
-      <c r="D85" s="33" t="n"/>
-      <c r="E85" s="33" t="n"/>
-      <c r="F85" s="33" t="n"/>
-      <c r="G85" s="33" t="n"/>
-      <c r="H85" s="33" t="n"/>
-      <c r="I85" s="33" t="n"/>
+      <c r="C85" s="45" t="n"/>
+      <c r="D85" s="45" t="n"/>
+      <c r="E85" s="45" t="n"/>
+      <c r="F85" s="45" t="n"/>
+      <c r="G85" s="45" t="n"/>
+      <c r="H85" s="45" t="n"/>
+      <c r="I85" s="46" t="n"/>
     </row>
   </sheetData>
   <autoFilter ref="A7:I74"/>

--- a/filesystem/MarketingOps/Org/client_services_org_chart.xlsx
+++ b/filesystem/MarketingOps/Org/client_services_org_chart.xlsx
@@ -973,14 +973,14 @@
         </is>
       </c>
       <c r="G8" s="28" t="n">
-        <v>45000</v>
+        <v>45474</v>
       </c>
       <c r="H8" s="28" t="n">
-        <v>45730</v>
+        <v>46204</v>
       </c>
       <c r="I8" s="29" t="inlineStr">
         <is>
-          <t>Renewed 03/15/2025; ongoing under Thornfield rate card.</t>
+          <t>Renewed 07/01/2024; ongoing under Thornfield rate card.</t>
         </is>
       </c>
     </row>
@@ -1059,10 +1059,10 @@
         </is>
       </c>
       <c r="G10" s="28" t="n">
-        <v>45108</v>
+        <v>45378</v>
       </c>
       <c r="H10" s="28" t="n">
-        <v>45838</v>
+        <v>46108</v>
       </c>
       <c r="I10" s="29" t="inlineStr">
         <is>

--- a/filesystem/MarketingOps/Org/client_services_org_chart.xlsx
+++ b/filesystem/MarketingOps/Org/client_services_org_chart.xlsx
@@ -1012,7 +1012,7 @@
       </c>
       <c r="F9" s="33" t="inlineStr">
         <is>
-          <t>% of managed spend (12%)</t>
+          <t>Flat monthly retainer $15,360</t>
         </is>
       </c>
       <c r="G9" s="34" t="n">
@@ -1551,7 +1551,7 @@
       </c>
       <c r="B22" s="25" t="inlineStr">
         <is>
-          <t>Larkspur Diagnostics</t>
+          <t>Larkfield Diagnostics</t>
         </is>
       </c>
       <c r="C22" s="26" t="inlineStr">

--- a/filesystem/MarketingOps/Org/client_services_org_chart.xlsx
+++ b/filesystem/MarketingOps/Org/client_services_org_chart.xlsx
@@ -1465,7 +1465,7 @@
       </c>
       <c r="B20" s="25" t="inlineStr">
         <is>
-          <t>Meridian Molecular</t>
+          <t>Bellhaven Molecular</t>
         </is>
       </c>
       <c r="C20" s="26" t="inlineStr">
